--- a/exports/trend_1d/HYUNDAI_full_report.xlsx
+++ b/exports/trend_1d/HYUNDAI_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>12.27</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45678</v>
+        <v>45679</v>
       </c>
       <c r="H2" t="n">
-        <v>1745.55</v>
+        <v>1702.5</v>
       </c>
       <c r="I2" t="n">
         <v>1745.540243646445</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.52</v>
+        <v>-6.88</v>
       </c>
       <c r="L2" t="n">
-        <v>7.64</v>
+        <v>7.84</v>
       </c>
       <c r="M2" t="n">
         <v>2.98</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.44</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45689</v>
+        <v>45691</v>
       </c>
       <c r="H3" t="n">
-        <v>1750.45</v>
+        <v>1799.9</v>
       </c>
       <c r="I3" t="n">
         <v>1773.456445969253</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.82</v>
+        <v>-5.72</v>
       </c>
       <c r="L3" t="n">
         <v>7.48</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.39</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H4" t="n">
-        <v>1715.4</v>
+        <v>1674.5</v>
       </c>
       <c r="I4" t="n">
         <v>1687.856121967889</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.69</v>
+        <v>-6.97</v>
       </c>
       <c r="L4" t="n">
         <v>7.99</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>11.93</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H5" t="n">
-        <v>1697.6</v>
+        <v>1759</v>
       </c>
       <c r="I5" t="n">
         <v>1747.829449106052</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.38</v>
+        <v>-5.05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.24</v>
+        <v>5.45</v>
       </c>
       <c r="M5" t="n">
         <v>2.02</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>11.45</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="H6" t="n">
-        <v>2507.6</v>
+        <v>2480.8</v>
       </c>
       <c r="I6" t="n">
         <v>2497.778633453635</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K6" t="n">
-        <v>42.56</v>
+        <v>41.03</v>
       </c>
       <c r="L6" t="n">
         <v>12.35</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>132</v>
+        <v>133</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.13</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="H7" t="n">
-        <v>1852.5</v>
+        <v>1902.8</v>
       </c>
       <c r="I7" t="n">
         <v>1895.148499210476</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K7" t="n">
-        <v>25.33</v>
+        <v>23.3</v>
       </c>
       <c r="L7" t="n">
         <v>2.77</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>7</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>11.83</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="H8" t="n">
-        <v>2144</v>
+        <v>2101</v>
       </c>
       <c r="I8" t="n">
         <v>2120.305851050629</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K8" t="n">
-        <v>12.68</v>
+        <v>10.42</v>
       </c>
       <c r="L8" t="n">
         <v>7.5</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -957,6 +1064,14 @@
       <c r="Q9" t="n">
         <v>25</v>
       </c>
+      <c r="R9" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1937,7 +2052,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6">
@@ -1947,7 +2062,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7">
@@ -1957,7 +2072,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8">
@@ -1967,7 +2082,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -1977,7 +2092,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>174.5</v>
+        <v>175.5</v>
       </c>
     </row>
     <row r="10">
@@ -1987,7 +2102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>192.4</v>
+        <v>194.2</v>
       </c>
     </row>
     <row r="11">
@@ -2027,7 +2142,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9.59</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="15">
@@ -2037,7 +2152,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11.51</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="16">
@@ -2047,7 +2162,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7.04</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="17">
@@ -2057,7 +2172,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>42.56</v>
+        <v>41.03</v>
       </c>
     </row>
     <row r="18">
@@ -2077,7 +2192,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.85</v>
+        <v>7.34</v>
       </c>
     </row>
     <row r="20">
@@ -2107,7 +2222,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
